--- a/Heuristic/data/real/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/real/production_capacity_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Scenario_pairs_generation\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/real/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{021E61DE-0394-4B76-8D7E-D899CF0D1B3F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16284" yWindow="-108" windowWidth="16536" windowHeight="8712" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -445,9 +445,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +485,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -517,7 +520,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -552,7 +555,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -587,7 +590,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -622,7 +625,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -657,7 +660,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -692,7 +695,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -727,7 +730,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -762,7 +765,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -797,7 +800,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -832,7 +835,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -867,7 +870,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -902,7 +905,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -937,7 +940,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -972,7 +975,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1015,9 +1018,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1087,7 +1090,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1160,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1227,7 +1230,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1297,7 +1300,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1542,7 +1545,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1585,9 +1588,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1657,7 +1660,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1692,7 +1695,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1762,7 +1765,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1797,7 +1800,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1832,7 +1835,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1867,7 +1870,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1902,7 +1905,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1937,7 +1940,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1972,7 +1975,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2007,7 +2010,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2042,7 +2045,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2112,7 +2115,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2155,9 +2158,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2297,7 +2300,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2332,7 +2335,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2367,7 +2370,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2507,7 +2510,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2542,7 +2545,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2577,7 +2580,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2612,7 +2615,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2647,7 +2650,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2682,7 +2685,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2725,9 +2728,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2762,7 +2765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2797,7 +2800,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2832,7 +2835,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2867,7 +2870,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2902,7 +2905,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2937,7 +2940,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2972,7 +2975,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3042,7 +3045,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3077,7 +3080,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3112,7 +3115,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3147,7 +3150,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3182,7 +3185,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3217,7 +3220,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3252,7 +3255,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3295,9 +3298,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3332,7 +3335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3367,7 +3370,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3507,7 +3510,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3577,7 +3580,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3612,7 +3615,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3647,7 +3650,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3682,7 +3685,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3717,7 +3720,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3787,7 +3790,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3865,9 +3868,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3937,7 +3940,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3972,7 +3975,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4007,7 +4010,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4112,7 +4115,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4147,7 +4150,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4182,7 +4185,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4252,7 +4255,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4287,7 +4290,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4322,7 +4325,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4357,7 +4360,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4392,7 +4395,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4435,9 +4438,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4472,7 +4475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4507,7 +4510,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4542,7 +4545,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4577,7 +4580,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4717,7 +4720,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4752,7 +4755,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4787,7 +4790,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4822,7 +4825,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4857,7 +4860,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4892,7 +4895,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4927,7 +4930,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4962,7 +4965,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -5005,9 +5008,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5042,7 +5045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5077,7 +5080,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5147,7 +5150,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5217,7 +5220,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5287,7 +5290,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -5357,7 +5360,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -5427,7 +5430,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -5462,7 +5465,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -5497,7 +5500,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -5532,7 +5535,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -5575,9 +5578,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5612,7 +5615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5647,7 +5650,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5682,7 +5685,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5717,7 +5720,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5752,7 +5755,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5787,7 +5790,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5822,7 +5825,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -5857,7 +5860,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -5892,7 +5895,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -5927,7 +5930,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -5962,7 +5965,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -5997,7 +6000,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -6032,7 +6035,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -6067,7 +6070,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -6102,7 +6105,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6145,9 +6148,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6217,7 +6220,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6287,7 +6290,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6357,7 +6360,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6392,7 +6395,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6427,7 +6430,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -6497,7 +6500,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -6532,7 +6535,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -6567,7 +6570,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -6602,7 +6605,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -6637,7 +6640,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6715,9 +6718,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6752,7 +6755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6787,7 +6790,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6857,7 +6860,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6892,7 +6895,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6927,7 +6930,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6962,7 +6965,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -6997,7 +7000,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -7032,7 +7035,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -7067,7 +7070,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -7102,7 +7105,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -7137,7 +7140,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -7172,7 +7175,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -7207,7 +7210,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7242,7 +7245,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7285,9 +7288,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7322,7 +7325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7357,7 +7360,7 @@
         <v>11566504</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7392,7 +7395,7 @@
         <v>58835934</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7427,7 +7430,7 @@
         <v>91543658</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>18072230</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7497,7 +7500,7 @@
         <v>247328536</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -7532,7 +7535,7 @@
         <v>19218363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -7567,7 +7570,7 @@
         <v>340144028</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>121459282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -7637,7 +7640,7 @@
         <v>65553281</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -7672,7 +7675,7 @@
         <v>85486578</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -7707,7 +7710,7 @@
         <v>68867596</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -7742,7 +7745,7 @@
         <v>16311248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -7777,7 +7780,7 @@
         <v>125875461</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -7812,7 +7815,7 @@
         <v>131144149</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7855,9 +7858,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7892,7 +7895,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7927,7 +7930,7 @@
         <v>7711003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7962,7 +7965,7 @@
         <v>39223956</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7997,7 +8000,7 @@
         <v>61029105</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8032,7 +8035,7 @@
         <v>12048153</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8067,7 +8070,7 @@
         <v>164885690</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -8102,7 +8105,7 @@
         <v>12812242</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -8137,7 +8140,7 @@
         <v>226762686</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -8172,7 +8175,7 @@
         <v>80972855</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -8207,7 +8210,7 @@
         <v>43702188</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -8242,7 +8245,7 @@
         <v>56991052</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -8277,7 +8280,7 @@
         <v>45911731</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -8312,7 +8315,7 @@
         <v>10874165</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -8347,7 +8350,7 @@
         <v>83916974</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -8382,7 +8385,7 @@
         <v>87429432</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>

--- a/Heuristic/data/real/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/real/production_capacity_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/real/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{021E61DE-0394-4B76-8D7E-D899CF0D1B3F}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D44953-B454-4206-9736-D7B9B6CCFC45}"/>
   <bookViews>
-    <workbookView xWindow="16284" yWindow="-108" windowWidth="16536" windowHeight="8712" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,20 @@
     <sheet name="other_scenario" sheetId="13" r:id="rId13"/>
     <sheet name="other_scenario_scaled" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -87,7 +100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +112,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBBBBBB"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -137,11 +156,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -157,6 +178,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,10 +469,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -489,34 +517,34 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>7711003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>7711003</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>7711003</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>7711003</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>7711003</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>7711003</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>7711003</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7711003</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>7711003</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>7711003</v>
       </c>
     </row>
@@ -524,34 +552,34 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>39223956</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>39223956</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>39223956</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>39223956</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>39223956</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>39223956</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>39223956</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>39223956</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>39223956</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>39223956</v>
       </c>
     </row>
@@ -559,34 +587,34 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>61029105</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>61029105</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>61029105</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>61029105</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>61029105</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>61029105</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>61029105</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>61029105</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>61029105</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>61029105</v>
       </c>
     </row>
@@ -594,34 +622,34 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>12048153</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>12048153</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>12048153</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>12048153</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>12048153</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>12048153</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>12048153</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>12048153</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>12048153</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>12048153</v>
       </c>
     </row>
@@ -629,34 +657,34 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>164885690</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>164885690</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>164885690</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>164885690</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>164885690</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>164885690</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>164885690</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>164885690</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>164885690</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>164885690</v>
       </c>
     </row>
@@ -664,34 +692,34 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>12812242</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>12812242</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>12812242</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>12812242</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>12812242</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>12812242</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>12812242</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>12812242</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>12812242</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>12812242</v>
       </c>
     </row>
@@ -699,34 +727,34 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>226762686</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>226762686</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>226762686</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>226762686</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>226762686</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>226762686</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>226762686</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>226762686</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>226762686</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>226762686</v>
       </c>
     </row>
@@ -734,34 +762,34 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>80972855</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>80972855</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>80972855</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>80972855</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>80972855</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>80972855</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>80972855</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>80972855</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>80972855</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>80972855</v>
       </c>
     </row>
@@ -769,34 +797,34 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>43702188</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>43702188</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>43702188</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>43702188</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>43702188</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>43702188</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>43702188</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>43702188</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>43702188</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>43702188</v>
       </c>
     </row>
@@ -804,34 +832,34 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>56991052</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>56991052</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>56991052</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>56991052</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>56991052</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>56991052</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>56991052</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>56991052</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>56991052</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>56991052</v>
       </c>
     </row>
@@ -839,34 +867,34 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>45911731</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>45911731</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>45911731</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>45911731</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>45911731</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>45911731</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>45911731</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>45911731</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>45911731</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>45911731</v>
       </c>
     </row>
@@ -874,34 +902,34 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>10874165</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>10874165</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>10874165</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>10874165</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>10874165</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>10874165</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>10874165</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>10874165</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>10874165</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>10874165</v>
       </c>
     </row>
@@ -909,34 +937,34 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>83916974</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>83916974</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>83916974</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>83916974</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>83916974</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>83916974</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>83916974</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>83916974</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>83916974</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>83916974</v>
       </c>
     </row>
@@ -944,34 +972,34 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>87429432</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>87429432</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>87429432</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>87429432</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>87429432</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>87429432</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>87429432</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>87429432</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>87429432</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>87429432</v>
       </c>
     </row>
@@ -979,36 +1007,42 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>587114096</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>587114096</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>587114096</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>587114096</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>587114096</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>587114096</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>587114096</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>587114096</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>587114096</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>587114096</v>
       </c>
+    </row>
+    <row r="17" spans="6:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
